--- a/jogos_2025-05-13.xlsx
+++ b/jogos_2025-05-13.xlsx
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Urooba</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8.5</v>
+        <v>1.67</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>4.33</v>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="P4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['5', '49']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>2.75</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['36', '43']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.22</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45790.46527777778</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Urooba</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.67</v>
       </c>
-      <c r="M5" t="n">
+      <c r="R5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="N5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['36', '43']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AI5" t="n">
         <v>4</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['5', '49']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.75</v>
+        <v>1.22</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45790.46527777778</v>
@@ -1536,119 +1536,119 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59', '67']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '17', '42']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45790.58333333334</v>
@@ -1794,119 +1794,119 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['45+10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45790.58333333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.88</v>
       </c>
       <c r="R12" t="n">
         <v>1.33</v>
@@ -1992,50 +1992,50 @@
         <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['59', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['3', '17', '42']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45790.58333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2091,80 +2091,80 @@
         <v>4.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>5.95</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="X13" t="n">
-        <v>3.8</v>
+        <v>2.66</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>4.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['45+10']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AI13" t="n">
         <v>2.88</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45790.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.58</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76', '78', '87', '90+1']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45790.64583333334</v>
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.61</v>
+        <v>1.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.06</v>
+        <v>4.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.78</v>
+        <v>6.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="P18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AA18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['14', '29', '45+3']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.29</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45790.64583333334</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="M19" t="n">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X19" t="n">
         <v>3.25</v>
       </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.75</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,13 +2929,13 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AJ19" t="n">
         <v>2.25</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.81</v>
+        <v>2.61</v>
       </c>
       <c r="M21" t="n">
-        <v>3.64</v>
+        <v>3.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="Y21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['16']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45790.64583333334</v>
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>3.09</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>3.17</v>
       </c>
       <c r="N23" t="n">
-        <v>6.2</v>
+        <v>2.32</v>
       </c>
       <c r="O23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.91</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['11', '75']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.38</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['14', '29', '45+3']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AI23" t="n">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.33</v>
+        <v>1.91</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45790.64583333334</v>
@@ -3610,22 +3610,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="M25" t="n">
-        <v>3.12</v>
+        <v>3.64</v>
       </c>
       <c r="N25" t="n">
-        <v>3.12</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AC25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD25" t="n">
         <v>2</v>
       </c>
-      <c r="AD25" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['25', '81']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45790.64583333334</v>
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,22 +3894,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.09</v>
+        <v>2.57</v>
       </c>
       <c r="M27" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="N27" t="n">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
         <v>1.5</v>
@@ -3918,25 +3918,25 @@
         <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V27" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
         <v>4.2</v>
@@ -3957,20 +3957,20 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['11', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.48</v>
       </c>
-      <c r="AH27" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AI27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.91</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45790.64583333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.46</v>
+        <v>2.33</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>3.12</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>3.12</v>
       </c>
       <c r="O28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P28" t="n">
         <v>1.95</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['25', '81']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['45+3']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['76', '78', '87', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['18']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>2.8</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45790.64583333334</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.41</v>
+        <v>1.48</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>2.85</v>
+        <v>6.2</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.4</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4602,20 +4602,20 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.05</v>
+        <v>3.7</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45790.89583333334</v>
@@ -4642,109 +4642,109 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M33" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>2.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>9.5</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.3</v>
       </c>
-      <c r="X33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC33" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['30', '65', '81', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AJ33" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45790.89583333334</v>
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="N34" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="O34" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W34" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AA34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['30', '65', '81', '90']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>3.7</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45790.89583333334</v>
